--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.69802080710481</v>
+        <v>2.063428381154532</v>
       </c>
       <c r="D2" t="n">
-        <v>11.99146686349852</v>
+        <v>1.948613365318509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6273328699845395</v>
+        <v>0.1019415913724877</v>
       </c>
       <c r="F2" t="n">
-        <v>1.000850250517306</v>
+        <v>0.1626381657090623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.95268654707389</v>
+        <v>2.267311563899507</v>
       </c>
       <c r="D3" t="n">
-        <v>13.99316736453313</v>
+        <v>2.273889696736634</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6273328699845395</v>
+        <v>0.1019415913724877</v>
       </c>
       <c r="F3" t="n">
-        <v>1.000850250517306</v>
+        <v>0.1626381657090623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
